--- a/Sportsrecruits Export Front Rush File Handling/SportsRecruits-FrontRush Export-Import Data Dictionary.xlsx
+++ b/Sportsrecruits Export Front Rush File Handling/SportsRecruits-FrontRush Export-Import Data Dictionary.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Jupyter Notebooks\SportsRecruits Export FrontRush Conversion\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\GitHub\Data-Project-Portfolio\Sportsrecruits Export Front Rush File Handling\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6F43750-C863-4C5B-84FD-0653281DCD90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C1D74EE-B51A-4B1E-804F-9D2CCBF978AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18645" yWindow="2520" windowWidth="30900" windowHeight="15705" xr2:uid="{475B49AA-AFB5-43F4-986C-2B1AEAF3AF3E}"/>
+    <workbookView xWindow="5670" yWindow="4005" windowWidth="25215" windowHeight="15780" xr2:uid="{475B49AA-AFB5-43F4-986C-2B1AEAF3AF3E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="90">
   <si>
     <t>Sportsrecruits field</t>
   </si>
@@ -306,6 +306,9 @@
   </si>
   <si>
     <t>*sum SAT Math + SAT Reading and Writing</t>
+  </si>
+  <si>
+    <t>Athlete Sex/Gender</t>
   </si>
 </sst>
 </file>
@@ -349,9 +352,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -686,7 +690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26F19105-0E9F-48CE-A824-863A228D6D13}">
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.7109375" bestFit="1" customWidth="1"/>
@@ -698,7 +702,7 @@
       <c r="A1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>86</v>
       </c>
     </row>
@@ -1029,62 +1033,67 @@
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>63</v>
+      <c r="A41" s="2" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
         <v>75</v>
       </c>
     </row>
